--- a/output/pdf_financials_xlsx/DMGI.xlsx
+++ b/output/pdf_financials_xlsx/DMGI.xlsx
@@ -4823,28 +4823,28 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.0135</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.0235</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.0235</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.0235</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.08511000000000001</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.08511000000000001</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>5.229701</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>6.014301</v>
       </c>
       <c r="K92" s="3" t="n">
         <v>0</v>
@@ -12062,7 +12062,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -13352,7 +13356,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -14318,7 +14326,11 @@
           <t>Reserves (Note 4)</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -14800,7 +14812,11 @@
           <t>Reserves (Note 4)</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -15207,7 +15223,11 @@
           <t>Reserves (Note 4)</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DMGI.xlsx
+++ b/output/pdf_financials_xlsx/DMGI.xlsx
@@ -844,16 +844,16 @@
         <v>18.342682</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>41.715043</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>46.528688</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>48.476591</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>56.437531</v>
       </c>
     </row>
     <row r="11">
@@ -890,7 +890,7 @@
         <v>-8.239917</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>43.236152</v>
+        <v>1.521109</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>-18.587693</v>
@@ -915,16 +915,16 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000133</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000404</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.002614</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000107</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1659,16 +1659,16 @@
         <v>-0.021508</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.052214</v>
+        <v>-0.052347</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.047701</v>
+        <v>-0.048105</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.197574</v>
+        <v>-0.200188</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.027779</v>
+        <v>-0.027886</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.922865</v>
@@ -1751,16 +1751,16 @@
         <v>-0.021508</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.052214</v>
+        <v>-0.052347</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.047701</v>
+        <v>-0.048105</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.197574</v>
+        <v>-0.200188</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.027779</v>
+        <v>-0.027886</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.519666</v>
@@ -1980,13 +1980,13 @@
         <v>0.002829</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.000343</v>
+        <v>0.49264</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>12.00418</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.133429</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>1.247513</v>
@@ -2076,13 +2076,13 @@
         <v>0.002829</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.000343</v>
+        <v>0.49264</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>12.00418</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.133429</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>1.649055</v>
@@ -2652,25 +2652,25 @@
         <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.06662800000000001</v>
+        <v>0.262242</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.521855</v>
+        <v>4.095454</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.450555</v>
+        <v>4.698646</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.258289</v>
+        <v>9.614962</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.193512</v>
+        <v>20.787219</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.337042</v>
+        <v>34.664745</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.330077</v>
+        <v>63.917585</v>
       </c>
     </row>
     <row r="49">
@@ -6303,16 +6303,16 @@
         <v>0</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.237907</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.224717</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.152996</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.099158</v>
       </c>
       <c r="N124" s="3" t="n">
         <v>0</v>
@@ -6349,16 +6349,16 @@
         <v>0</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.237907</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.224717</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.152996</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.099158</v>
       </c>
       <c r="N125" s="3" t="n">
         <v>0</v>
@@ -7230,7 +7230,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -10687,7 +10687,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19870,7 +19870,11 @@
           <t>Principal lease payments</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -28038,7 +28042,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -31400,7 +31404,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -38351,7 +38355,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">

--- a/output/pdf_financials_xlsx/DMGI.xlsx
+++ b/output/pdf_financials_xlsx/DMGI.xlsx
@@ -1720,13 +1720,13 @@
         <v>0.403199</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.661566</v>
+        <v>0.136567</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1.71596</v>
+        <v>0.205113</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>19.824751</v>
+        <v>0.042388</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>21.902282</v>
@@ -1766,13 +1766,13 @@
         <v>-0.519666</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-35.658932</v>
+        <v>-36.183931</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-14.275545</v>
+        <v>-15.786392</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>2.849355</v>
+        <v>-16.933008</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>5.440554</v>
@@ -1824,13 +1824,13 @@
         <v>-61.11373755477311</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-310.985124157509</v>
+        <v>-315.5636931173861</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-141.3033461631543</v>
+        <v>-156.2581332932123</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>6.590214133764725</v>
+        <v>-39.16400330908264</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>19.47158288385936</v>
@@ -5190,13 +5190,13 @@
         <v>0</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.136567</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.205113</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.042388</v>
       </c>
       <c r="L100" s="3" t="n">
         <v>0</v>
@@ -20423,7 +20423,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -21632,7 +21632,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -32526,7 +32526,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -34296,7 +34296,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">

--- a/output/pdf_financials_xlsx/DMGI.xlsx
+++ b/output/pdf_financials_xlsx/DMGI.xlsx
@@ -5334,16 +5334,16 @@
         <v>-2.066825</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0</v>
+        <v>0.143644</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>0</v>
+        <v>0.045973</v>
       </c>
       <c r="M103" s="3" t="n">
-        <v>0</v>
+        <v>-0.14853</v>
       </c>
       <c r="N103" s="3" t="n">
-        <v>0</v>
+        <v>-0.593112</v>
       </c>
     </row>
     <row r="104">
@@ -5472,16 +5472,16 @@
         <v>0.347321</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>-6.149406</v>
+        <v>-6.005762</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>2.724275</v>
+        <v>2.770248</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>-0.943998</v>
+        <v>-1.092528</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0.741783</v>
+        <v>0.148671</v>
       </c>
     </row>
     <row r="107">
@@ -5656,16 +5656,16 @@
         <v>0</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.015843</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.05257</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.031003</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.014981</v>
       </c>
     </row>
     <row r="111">
@@ -5941,7 +5941,7 @@
         <v>0</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>0</v>
+        <v>-1.181414</v>
       </c>
     </row>
     <row r="117">
@@ -15630,7 +15630,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -16951,7 +16955,11 @@
           <t>Prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -17816,7 +17824,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>PurchaseOfIntangibles</t>
+          <t>NetIntangiblesPurchaseAndSale</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -22440,7 +22448,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -35418,7 +35430,11 @@
           <t>Deferred income tax recovery 21</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E357" t="inlineStr">
         <is>
           <t>-</t>
@@ -37340,7 +37356,11 @@
           <t>Deferred income tax recovery 20</t>
         </is>
       </c>
-      <c r="D381" t="inlineStr"/>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E381" t="inlineStr">
         <is>
           <t>-</t>
